--- a/data/timisoara/service_status.xlsx
+++ b/data/timisoara/service_status.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H81"/>
+  <dimension ref="A1:H121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3002,8 +3002,6 @@
           <t>Servis</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr"/>
-      <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
         <is>
           <t>Toplu servise alındı</t>
@@ -3015,6 +3013,1292 @@
         </is>
       </c>
       <c r="H81" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>1001</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Servis Dışı</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Bogie</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Dişli Kutusu</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>2026-04-05 16:03:43</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>1002</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:44:22</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>1003</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:44:22</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>1004</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:44:22</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>1005</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:44:22</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>1006</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:44:22</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>1007</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:44:22</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>1008</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:44:23</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>1009</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:44:23</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>1010</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:44:23</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>1011</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:44:23</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>1012</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:44:23</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>1013</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:44:23</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>1014</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:44:23</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>1015</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:44:23</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>1016</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:44:23</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>1017</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:44:23</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>1018</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:44:23</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>1019</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:44:23</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>1020</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:44:23</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>1021</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:44:23</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>1022</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:44:24</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>1023</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:44:24</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>1024</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:44:24</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>1025</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:44:24</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>1026</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:44:24</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>1027</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:44:24</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>1028</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:44:24</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>1029</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:44:24</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>1030</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:44:24</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>1031</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:44:24</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>1032</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:44:24</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>1033</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:44:24</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>1034</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:44:25</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>1035</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:44:25</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>1036</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:44:25</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>1037</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:44:25</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>1038</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:44:25</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>1039</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:44:25</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>1040</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>2026-04-05 15:44:25</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
         <is>
           <t>admin</t>
         </is>

--- a/data/timisoara/service_status.xlsx
+++ b/data/timisoara/service_status.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H121"/>
+  <dimension ref="A1:H122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3044,7 +3044,6 @@
           <t>Dişli Kutusu</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
         <is>
           <t>2026-04-05 16:03:43</t>
@@ -4299,6 +4298,40 @@
         </is>
       </c>
       <c r="H121" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>1001</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Servis Dışı</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Bogie</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr"/>
+      <c r="F122" t="inlineStr"/>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>2026-04-06 16:32:37</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
         <is>
           <t>admin</t>
         </is>

--- a/data/timisoara/service_status.xlsx
+++ b/data/timisoara/service_status.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H122"/>
+  <dimension ref="A1:H162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4324,14 +4324,1298 @@
           <t>Bogie</t>
         </is>
       </c>
-      <c r="E122" t="inlineStr"/>
-      <c r="F122" t="inlineStr"/>
       <c r="G122" t="inlineStr">
         <is>
           <t>2026-04-06 16:32:37</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>1001</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Servis Dışı</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Auxiliary_Power_Unit</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>DBS Şalteri</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr"/>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>2026-04-09 00:35:51</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>1002</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>2026-04-09 00:25:00</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>1003</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>2026-04-09 00:25:00</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>1004</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>2026-04-09 00:25:00</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>1005</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>2026-04-09 00:25:01</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>1006</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>2026-04-09 00:25:01</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>1007</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>2026-04-09 00:25:01</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>1008</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>2026-04-09 00:25:02</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>1009</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>2026-04-09 00:25:02</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>1010</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>2026-04-09 00:25:02</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>1011</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>2026-04-09 00:25:02</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>1012</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>2026-04-09 00:25:03</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>1013</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>2026-04-09 00:25:03</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>1014</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>2026-04-09 00:25:04</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>1015</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>2026-04-09 00:25:04</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>1016</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>2026-04-09 00:25:04</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>1017</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>2026-04-09 00:25:05</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>1018</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>2026-04-09 00:25:05</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>1019</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>2026-04-09 00:25:05</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>1020</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>2026-04-09 00:25:06</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>1021</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>2026-04-09 00:25:06</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>1022</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>2026-04-09 00:25:06</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>1023</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>2026-04-09 00:25:07</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>1024</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>2026-04-09 00:25:07</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>1025</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>2026-04-09 00:25:07</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>1026</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>2026-04-09 00:25:08</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>1027</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>2026-04-09 00:25:08</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>1028</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>2026-04-09 00:25:08</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>1029</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>2026-04-09 00:25:09</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>1030</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>2026-04-09 00:25:09</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>1031</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>2026-04-09 00:25:09</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>1032</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>2026-04-09 00:25:09</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>1033</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>2026-04-09 00:25:10</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>1034</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>2026-04-09 00:25:10</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>1035</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>2026-04-09 00:25:10</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>1036</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>2026-04-09 00:25:10</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>1037</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>2026-04-09 00:25:11</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>1038</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>2026-04-09 00:25:11</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>1039</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>2026-04-09 00:25:11</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>1040</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>2026-04-09 00:25:12</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
         <is>
           <t>admin</t>
         </is>

--- a/data/timisoara/service_status.xlsx
+++ b/data/timisoara/service_status.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H162"/>
+  <dimension ref="A1:H245"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4361,7 +4361,6 @@
           <t>DBS Şalteri</t>
         </is>
       </c>
-      <c r="F123" t="inlineStr"/>
       <c r="G123" t="inlineStr">
         <is>
           <t>2026-04-09 00:35:51</t>
@@ -5122,22 +5121,22 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Servis</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>Toplu servise alındı</t>
+          <t>Servis Dışı</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>HSCB</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>2026-04-09 00:25:07</t>
+          <t>2026-04-09 10:41:54</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>admin</t>
+          <t>kozek</t>
         </is>
       </c>
     </row>
@@ -5616,6 +5615,2638 @@
         </is>
       </c>
       <c r="H162" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>1001</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Servis Dışı</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Auxiliary_Power_Unit</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>DBS Şalteri</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>2026-04-09 10:28:28</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>kozek</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>1001</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Servis Dışı</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Auxiliary_Power_Unit</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>DBS Şalteri</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>2026-04-09 10:35:05</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>kozek</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>1002</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>2026-04-09 10:33:21</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>kozek</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>1003</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>2026-04-09 10:33:22</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>kozek</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>1004</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>2026-04-09 10:33:22</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>kozek</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>1005</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>2026-04-09 10:33:22</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>kozek</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>1006</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>İşletme Kaynaklı Servis Dışı</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>2026-04-09 10:36:30</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>kozek</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>1007</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>2026-04-09 10:33:23</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>kozek</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>1008</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>İşletme Kaynaklı Servis Dışı</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>2026-04-09 10:37:08</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>kozek</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>1009</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>2026-04-09 10:33:24</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>kozek</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>1010</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>2026-04-09 10:33:24</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>kozek</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>1011</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>2026-04-09 10:33:24</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>kozek</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>1012</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>2026-04-09 10:33:25</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>kozek</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>1013</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>2026-04-09 10:33:25</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>kozek</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>1014</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>İşletme Kaynaklı Servis Dışı</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>2026-04-09 10:38:41</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>kozek</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>1015</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>İşletme Kaynaklı Servis Dışı</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>2026-04-09 10:38:55</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>kozek</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>1016</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>2026-04-09 10:33:26</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>kozek</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>1017</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>2026-04-09 10:33:27</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>kozek</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>1018</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>2026-04-09 10:33:27</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>kozek</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>1019</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>2026-04-09 10:33:28</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>kozek</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>1020</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>İşletme Kaynaklı Servis Dışı</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>2026-04-09 10:39:39</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>kozek</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>1021</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>2026-04-09 10:33:31</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>kozek</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>1022</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>2026-04-09 10:33:33</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>kozek</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>1023</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>2026-04-09 10:33:35</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>kozek</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>1024</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>2026-04-09 10:33:35</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>kozek</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>1025</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Servis Dışı</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>HSCB</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>2026-04-09 10:40:46</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>kozek</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>1026</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>2026-04-09 10:33:36</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>kozek</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>1027</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>İşletme Kaynaklı Servis Dışı</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>2026-04-09 10:42:39</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>kozek</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>1028</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>2026-04-09 10:33:36</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>kozek</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>1029</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>2026-04-09 10:33:36</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>kozek</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>1030</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>2026-04-09 10:33:37</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>kozek</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>1031</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>2026-04-09 10:33:37</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>kozek</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>1032</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>2026-04-09 10:33:38</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>kozek</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>1033</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>İşletme Kaynaklı Servis Dışı</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>2026-04-09 10:43:27</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>kozek</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>1034</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>2026-04-09 10:33:38</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>kozek</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>1035</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>2026-04-09 10:33:39</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>kozek</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>1036</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>2026-04-09 10:33:39</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>kozek</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>1037</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>İşletme Kaynaklı Servis Dışı</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>2026-04-09 10:43:53</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>kozek</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>1038</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>2026-04-09 10:33:40</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>kozek</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>1039</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>2026-04-09 10:33:40</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>kozek</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>1040</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>2026-04-09 10:33:40</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>kozek</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>1001</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Servis Dışı</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>Auxiliary_Power_Unit</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>DBS Şalteri</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>2026-04-09 10:50:21</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>kozek</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>1002</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>2026-04-09 10:47:36</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>kozek</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>1003</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>2026-04-09 10:47:36</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>kozek</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>1004</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>2026-04-09 10:47:37</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>kozek</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>1005</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>2026-04-09 10:47:37</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>kozek</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>1006</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>2026-04-09 10:47:38</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>kozek</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>1007</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>2026-04-09 10:47:38</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>kozek</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>1008</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>2026-04-09 10:47:38</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>kozek</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>1009</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>2026-04-09 10:47:39</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>kozek</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>1010</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>2026-04-09 10:47:39</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>kozek</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>1011</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>2026-04-09 10:47:40</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>kozek</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>1012</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>2026-04-09 10:47:40</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>kozek</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>1013</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>2026-04-09 10:47:40</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>kozek</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>1014</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>2026-04-09 10:47:41</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>kozek</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>1015</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>2026-04-09 10:47:41</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>kozek</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>1016</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>2026-04-09 10:47:41</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>kozek</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>1017</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>2026-04-09 10:47:42</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>kozek</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>1018</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>2026-04-09 10:47:42</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>kozek</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>1019</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>2026-04-09 10:47:43</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>kozek</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>1020</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>2026-04-09 10:47:43</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>kozek</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>1021</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>2026-04-09 10:47:43</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>kozek</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>1022</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>2026-04-09 10:47:44</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>kozek</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>1023</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>2026-04-09 10:47:44</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>kozek</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>1024</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>2026-04-09 10:47:44</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>kozek</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>1025</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>2026-04-09 10:47:45</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>kozek</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>1026</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>2026-04-09 10:47:45</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>kozek</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>1027</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>2026-04-09 10:47:45</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>kozek</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>1028</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>2026-04-09 10:47:46</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>kozek</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>1029</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>2026-04-09 10:47:46</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>kozek</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>1030</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>2026-04-09 10:47:47</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>kozek</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>1031</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>2026-04-09 10:47:47</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>kozek</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>1032</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>2026-04-09 10:47:47</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>kozek</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>1033</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>2026-04-09 10:47:48</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>kozek</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>1034</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>2026-04-09 10:47:48</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>kozek</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>1035</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>2026-04-09 10:47:49</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>kozek</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>1036</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>2026-04-09 10:47:49</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>kozek</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>1037</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>2026-04-09 10:47:49</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>kozek</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>1038</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>2026-04-09 10:47:50</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>kozek</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>1039</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>2026-04-09 10:47:50</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>kozek</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>1040</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>Toplu servise alındı</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>2026-04-09 10:47:51</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>kozek</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>1001</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Servis</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>2026-04-09 13:22:49</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>1002</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Servis Dışı</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>Traction_Converter</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>Tahrik Konvertörü Sis.  Batary charger</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr"/>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>2026-04-09 13:23:02</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
         <is>
           <t>admin</t>
         </is>

--- a/data/timisoara/service_status.xlsx
+++ b/data/timisoara/service_status.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H245"/>
+  <dimension ref="A1:H247"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8240,7 +8240,6 @@
           <t>Tahrik Konvertörü Sis.  Batary charger</t>
         </is>
       </c>
-      <c r="F245" t="inlineStr"/>
       <c r="G245" t="inlineStr">
         <is>
           <t>2026-04-09 13:23:02</t>
@@ -8249,6 +8248,77 @@
       <c r="H245" t="inlineStr">
         <is>
           <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>1001</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Servis Dışı</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>Pantograf</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>Pantograf Limit Switch</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>2026-04-14 09:49:44</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>1002</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>İşletme Kaynaklı Servis Dışı</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr"/>
+      <c r="E247" t="inlineStr"/>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>Kaza</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>2026-04-14 16:16:41</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>femecen</t>
         </is>
       </c>
     </row>
